--- a/samples/전략물자_판정DB.xlsx
+++ b/samples/전략물자_판정DB.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,75 +435,75 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SDR-100</v>
+        <v>VMC-850</v>
       </c>
       <c r="B3" t="str">
-        <v>해당</v>
+        <v>비해당</v>
       </c>
       <c r="C3" t="str">
-        <v>5A001</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>자가판정</v>
       </c>
       <c r="E3" t="str">
-        <v>2025-12-10</v>
+        <v>2026-02-01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HPA-9000</v>
+        <v>SDR-100</v>
       </c>
       <c r="B4" t="str">
         <v>해당</v>
       </c>
       <c r="C4" t="str">
-        <v>3A001</v>
+        <v>5A001</v>
       </c>
       <c r="D4" t="str">
-        <v>전문판정</v>
+        <v>자가판정</v>
       </c>
       <c r="E4" t="str">
-        <v>2025-10-15</v>
+        <v>2025-12-10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENC-55</v>
+        <v>HPA-9000</v>
       </c>
       <c r="B5" t="str">
         <v>해당</v>
       </c>
       <c r="C5" t="str">
-        <v>5A002</v>
+        <v>3A001</v>
       </c>
       <c r="D5" t="str">
         <v>전문판정</v>
       </c>
       <c r="E5" t="str">
-        <v>2025-09-20</v>
+        <v>2025-10-15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>PWC-12</v>
+        <v>ENC-55</v>
       </c>
       <c r="B6" t="str">
-        <v>비해당</v>
+        <v>해당</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>5A002</v>
       </c>
       <c r="D6" t="str">
-        <v>자가판정</v>
+        <v>전문판정</v>
       </c>
       <c r="E6" t="str">
-        <v>2025-11-05</v>
+        <v>2025-09-20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MM-200</v>
+        <v>PWC-12</v>
       </c>
       <c r="B7" t="str">
         <v>비해당</v>
@@ -515,12 +515,12 @@
         <v>자가판정</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-01-08</v>
+        <v>2025-11-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BRK-07</v>
+        <v>MM-200</v>
       </c>
       <c r="B8" t="str">
         <v>비해당</v>
@@ -535,9 +535,26 @@
         <v>2026-01-08</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BRK-07</v>
+      </c>
+      <c r="B9" t="str">
+        <v>비해당</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-01-08</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>